--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vincent Dusanek\Documents\GitHub\ai-rater-prompts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26A9A99-EB75-480A-82DE-18F6D710577E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290F7149-D201-4670-8BEE-FF750DBEAE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E4E8083B-D79D-4448-92F1-4C454AB4E1C3}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>beschreibung_vortrag</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <r>
       <rPr>
@@ -145,7 +142,7 @@
     <t xml:space="preserve">AG0EVJU2003FU  Notizen:     cognitive-load-theorie   = wie wir Lernmaterialien nutzen  wie Informationen aus dem Arbeitsgedächtnis verarbeitet werden, dies ist begrenzt  ungünstig: Hintergrundmusik, die nichts mit dem Lernenden zu tun hat  günstig: was man aufwendet, um neue Schemata zu lernen  Personen mit hoher inhaltsbedingte Belastung - ebenso hohe sachfremde B. - ist lernen kaum möglich   Personen mit niedriger inhaltsbedingte Belastung aufgrund von Vorwissen - ebenso niedrige sachfremde B. - Potenzial zum lernen lernen möglich   man soll darauf achten, dass sachfremde Belastung gering ist und keine Ablenkung von Hintergrundmusik      Eine exemplarische empirische Studie zur Cognitive-Load-Theory  2004 10 Hochschulstudenten erhielten Informationssystem zum Thema   Blutkreislauf   3 Webseiten:  1. visuelle Bilder + Text + ohne Hintergrundmusik  2. visuelle Bilder + Text + Hintergrundmusik  3. visuelle Bilder + Text vorgelesen + Hintergrundmusik    Wie lernen sie/ was nehmen sie mit? Wie ist Reaktionszeit auf Ton?   man lernt anscheinend mehr, wenn Bilder mit Ton vorhanden ist   bei nur visueller Informationen Hintergrundmusik relativ egal, bei zusätzlichen audio Informativen eher keine Hintergrundmusik    Das ICAP-Modell von Chi &amp; Wylie  passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen   körperlich aktive = wichtige Infos unterstreichen   konstruktiv = Mindmap erstellen  interaktiv = mit anderen austauschen -  am besten - neues wissen produzieren - tiefes Verständnis   also reines zuhören nicht so gut !  aber nur wenn Auseinandersetzung auch über das Lernende ist    Eine exemplarische empirische Studie zum ICAP-Modell  120 Studierende  zum Thema Chemie   Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest   interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten  daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !     Die Cognitive Theory of Multimedia Learning (CTML) von Mayer  welche Prozesse laufen ab, wenn wir Multimedia benutzen   Multimedia = bild + wörter meistens -&gt; sensorisches Gedächtnis -&gt; Arbeitsgedächtnis: alle Infos können wir nicht gleichzeitig aufnehmen  dann Integration mit Vorwissen -&gt; dann lernen     daher beide Kanäle ansprechen !  Überlastung eines der beiden Kanäle sollte vermieden werden!    Eine exemplarische empirische Studie zur Cognitive Theory of Multimedia Learning (CTML)  1: Bilder + geschriebener Text  2. Bilder + vorgelesener Text  danach Erinnerungstest   bildlicher Inhalt muss mit auditiven Inhalt passend sein! multimediales lernen ist besser!    Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten  Powerpointfolien im Vortrag - grafische Darstellung  Videos mit Text  Infos räumlich nah und relativ nah im zeitlichen abstand   Comic in einer ecke nicht gut, da so Aufmerksamkeit abgelenkt wird    Aufgabenstellung:     Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, auf welcher überwiegend Bilder zu sehen sind, welche ich gleichzeitig mit Worten erkläre. So wird die audio und visuelle Belastung angesprochen. Daher weniger Text, da man sich vorgelesenen Text besser merken kann (siehe Cognitive Theory of Multimedia). Zusätzlich würde ich anfangs auf Themen aus dem Unterricht oder ganz allgemeine Themen ansprechen, so dass jeder bei dem gleichen Wissenstand abgeholt werden kann bei gleicher inhaltsbedingter Belastung (siehe Cognitive-Load-Theory). Außerdem würde ich auch ein Video zeigen, welches das Gezeigte und Gesprochene noch einmal mit Hintergrundmusik wiederholt. Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.   daher würde ich alle Lernaktivitäten miteinander vereinen, um den bestmöglichen Vortrag zu haben.         </t>
   </si>
   <si>
-    <t>Antwort</t>
+    <t>Textfeld</t>
   </si>
 </sst>
 </file>
@@ -627,21 +624,19 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:2" ht="371.25" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="4"/>
     </row>
     <row r="3" spans="1:2" ht="303.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5"/>
     </row>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vincent Dusanek\Documents\GitHub\ai-rater-prompts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290F7149-D201-4670-8BEE-FF750DBEAE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E4283B-1466-4202-AD7D-9BF491A452CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E4E8083B-D79D-4448-92F1-4C454AB4E1C3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <r>
       <rPr>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>Textfeld</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
 </sst>
 </file>
@@ -615,30 +618,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D6E467-3641-4C92-A3EE-80450D709D04}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="113.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="113.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="371.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" ht="371.25" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:2" ht="303.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" ht="303.75" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vincent Dusanek\Documents\GitHub\ai-rater-prompts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E4283B-1466-4202-AD7D-9BF491A452CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025B0A2D-713B-4A7A-9419-7D3C21CA11DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E4E8083B-D79D-4448-92F1-4C454AB4E1C3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <rPr>
@@ -147,22 +147,22 @@
   <si>
     <t>Id</t>
   </si>
+  <si>
+    <t xml:space="preserve">AL0FRAP2004GR  Arbeitsgedächtnis kann nicht beliebig viele Informationen verarbeiten (7+/-2) -&gt; man sollte sich auf den Folien auf wichtigste Informationen beschränken; Folien nicht zu überfüllt gestalten, da man sich in erster Linie auf die Erklärungen des Vortragenden konzentrieren soll (Folien dienen der Unterstützung); Vorwissen berücksichtigen (Person mit geringem Vorwissen kann mit einem bestimmten Thema nicht so viel anfangen, wie eine Person mit viel Vorwissen -&gt; muss sich erst einmal mit der Materie auseinandersetzen -&gt; deswegen müssen Folien so gestaltet sein, dass sie dem Vorwissen der Adressaten gerecht werden (nicht zu komplex); zudem sollten sich auf den Folien keine unnötigen Bilder befinden (sachfremde kognitive Belastung gering halten) -&gt; Kohärenzprinzip =&gt; beinhaltet in Cognitive-Load-Theorie;   exemplarische empirische Studie zur Cognitive-Load-Theorie: wie in dieser Studie beschrieben wird, werden audiovisuell präsentierte Informationen besser behalten als die, die nur visuell präsentiert werden -&gt; Folien sollten nicht mit Text überfüllt sein, sondern lieber themenbezogene Bilder und wichtige Stichpunkte, die dann vom Vortragenden erläutert werden -&gt;Modalitätsprinzip  Cognitive Theory of Multimedia Learning: Lernen bedeutet aktive Informationsverarbeitung -&gt; Folien sollten nicht nur statisch gestaltet werden, sondern die Zuhörer auch mit einbeziehen -&gt; Interaktivitätsprinzip (gelernter Stoff soll in Kleingruppen nachbesprochen werden -&gt; hoher Lernerfolg); im Arbeitsgedächtnis müssen die aufgenommenen Informationen, die durch das Auge und das Ohr aufgenommen werden, selektiert werden -&gt; auf den Folien sollten beide Informationskanäle angesprochen werden, da ein tieferes Verständnis des Stoffes erreicht werden kann, aber eine Überlastung soll vermieden werden (nicht visuelle Informationen und geschriebenen Text kombinieren, sondern Bilder mit gesprochenem Text) -&gt; Multimediaprinzip (Präsentation des Inhalts in textueller und bildhafter Form, wobei sich der Inhalt aber nicht wiederholen darf, sondern sich ergänzen -&gt; Redundanzprinzip)  diese Aussagen belegt auch die exemplarische empirische Studie zur Cognitive Theory of Multimedia Learning; es kommt zu einer besseren Verteilung, wenn beide Kanäle angesprochen werden und die gelernten Inhalte können besser mit dem Vorwissen verknüpft werden  sinnvolle Lernaktivitäten: Interaktiv ist sinnvoll, da man sich hierbei vertieft mit dem Stoff auseinandersetzt, indem man in einer Diskussion Gründe für seine eigene Position äußert. Gleichzeitig wird man aber auch mit anderen Meinungen konfrontiert wird, denen man sich nicht entziehen, da sonst keine Diskussion zustande kommt. Hierbei lernt man verschiedene Sichtweisen zu einem Thema kennen. Zudem wird automatisch die eigene Position hinterfragt und eventuell auch korrigiert. Ein weiterer wichtiger Punkt ist, dass in einer Diskussion auch das Vorwissen angeregt wird, was wiederum zu einer stärkeren Verknüpfung der gelernten Inhalte führt, die länger im Gedächtnis präsent sind (Tiefenverständnis -&gt; in einer gelungenen Diskussion werden kognitive Prozesse anregt).  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A1annju2002st      </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -204,6 +204,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -214,18 +226,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFF7474"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -263,26 +275,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D6E467-3641-4C92-A3EE-80450D709D04}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="113.42578125" customWidth="1"/>
@@ -629,28 +708,479 @@
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3" ht="371.25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:3" ht="303.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" ht="303.75" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5"/>
+    </row>
+    <row r="5" spans="1:3" ht="236.25" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="6"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="6"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="6"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="6"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="6"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="6"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="6"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="7"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="8"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="9"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="8"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="9"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="8"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="9"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="8"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="9"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="8"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="9"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="8"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="9"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="8"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="9"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="8"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="9"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="8"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="9"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="8"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="9"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="8"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="9"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="8"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="9"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="8"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="9"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="8"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="9"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="8"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="9"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="8"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="9"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="8"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="9"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="8"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="9"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="8"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="9"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="8"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="9"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="8"/>
+    </row>
+    <row r="90" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="10"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="6"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="2"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="6"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="2"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="6"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="2"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="6"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="2"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="6"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="2"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="6"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="2"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="6"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="2"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="6"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="2"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="6"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="2"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="6"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="2"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="6"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="2"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="6"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="2"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="6"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="2"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="6"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="2"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="6"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="2"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="6"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="2"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="6"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="2"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="6"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="2"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="6"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="2"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="6"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="2"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="6"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="2"/>
+    </row>
+    <row r="133" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B133" s="11"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="2"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="6"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="2"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="6"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="2"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="6"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="2"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="6"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="2"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="6"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="2"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="6"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="2"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="6"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="2"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="6"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vincent Dusanek\Documents\GitHub\ai-rater-prompts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBA4561-6770-42A9-B807-BAAC94CAD12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467754EA-A3B6-44E0-AF41-4021977C04C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E4E8083B-D79D-4448-92F1-4C454AB4E1C3}"/>
   </bookViews>
